--- a/output/pdf_financials_xlsx/AEF.xlsx
+++ b/output/pdf_financials_xlsx/AEF.xlsx
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.0587</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.000272</v>
       </c>
     </row>
     <row r="92">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.550887</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.048516</v>
       </c>
     </row>
     <row r="119">
@@ -2552,7 +2552,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>-0.0587</v>
       </c>
@@ -2824,7 +2828,11 @@
           <t>Acquisition of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>-0.550887</v>
       </c>

--- a/output/pdf_financials_xlsx/AEF.xlsx
+++ b/output/pdf_financials_xlsx/AEF.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001559</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004845</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.163202</v>
+        <v>-0.164761</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.615497</v>
+        <v>-1.620342</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.163202</v>
+        <v>-0.164761</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.615497</v>
+        <v>-1.620342</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.176212</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.176212</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.9e-05</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.346952</v>
+        <v>0.17074</v>
       </c>
     </row>
     <row r="49">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">

--- a/output/pdf_financials_xlsx/AEF.xlsx
+++ b/output/pdf_financials_xlsx/AEF.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.072974</v>
+        <v>0.07553600000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.125644</v>
+        <v>0.166342</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.072974</v>
+        <v>0.07553600000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.125644</v>
+        <v>0.166342</v>
       </c>
     </row>
     <row r="11">
@@ -3116,7 +3116,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.002562</v>
       </c>
